--- a/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/AirlineRoute-KATL-KBOS.xlsx
+++ b/Airlines-Services/airlines/management/commands/AirlineRoutesWayPoints/AirlineRoute-KATL-KBOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\flight-profile\airline\management\commands\AirlineRoutesWayPoints\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\Airlines-Services\Airlines-Services\airlines\management\commands\AirlineRoutesWayPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24ACE33-8A69-4882-B6BD-D16B976264A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D742B8-AFA9-4E8D-8323-FE2B6A64065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -676,6 +676,7 @@
   <cols>
     <col min="2" max="2" width="8.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
